--- a/data/trans_orig/P6713-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6713-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2012</t>
+          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2012 (tasa de respuesta: 99,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7123</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7983</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26897</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28708</t>
+          <t>27509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27688</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50647</t>
+          <t>49617</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14584</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32255</t>
+          <t>31894</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>7832</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20763</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25807</t>
+          <t>26351</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48957</t>
+          <t>48269</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25659</t>
+          <t>24648</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44484</t>
+          <t>43201</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40768</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58627</t>
+          <t>59065</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>70260</t>
+          <t>70045</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>96957</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>9417</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27026</t>
+          <t>26969</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30395</t>
+          <t>29263</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25229</t>
+          <t>24142</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49730</t>
+          <t>48604</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31424</t>
+          <t>31023</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,82 +1541,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>18982</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>11468</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>28873</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>39088</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>27888</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>53972</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>8,21%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>18982</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>11790</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>29299</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>10,66%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>39088</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>27508</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>53220</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71013</t>
+          <t>69989</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103746</t>
+          <t>102202</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32433</t>
+          <t>31751</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>56822</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>110515</t>
+          <t>110233</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>151491</t>
+          <t>153368</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63671</t>
+          <t>62727</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94388</t>
+          <t>94486</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52518</t>
+          <t>54115</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82404</t>
+          <t>83520</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126979</t>
+          <t>125469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169290</t>
+          <t>169273</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162741</t>
+          <t>160233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>200405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108376</t>
+          <t>108650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141342</t>
+          <t>142802</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281951</t>
+          <t>278793</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>333454</t>
+          <t>332508</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,56%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27966</t>
+          <t>27798</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20616</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41849</t>
+          <t>43649</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>16928</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38707</t>
+          <t>39271</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10755</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28220</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31699</t>
+          <t>32372</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58462</t>
+          <t>57996</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72023</t>
+          <t>71643</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>105314</t>
+          <t>105641</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51197</t>
+          <t>51231</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78807</t>
+          <t>80495</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>131625</t>
+          <t>130769</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176062</t>
+          <t>176485</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91627</t>
+          <t>90066</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>126918</t>
+          <t>126691</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45766</t>
+          <t>47648</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74462</t>
+          <t>74920</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>145185</t>
+          <t>145752</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>191467</t>
+          <t>191053</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169284</t>
+          <t>168774</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211956</t>
+          <t>211386</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108129</t>
+          <t>105121</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>142667</t>
+          <t>141357</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>287210</t>
+          <t>289637</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>340820</t>
+          <t>343206</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27918</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19617</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42044</t>
+          <t>43169</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11128</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30336</t>
+          <t>28803</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28926</t>
+          <t>28888</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25966</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>51912</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>54495</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>85887</t>
+          <t>86176</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42301</t>
+          <t>42253</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>69848</t>
+          <t>68519</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>102477</t>
+          <t>102561</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>147554</t>
+          <t>144736</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68983</t>
+          <t>68157</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102379</t>
+          <t>103846</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29936</t>
+          <t>30339</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58197</t>
+          <t>58011</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>105582</t>
+          <t>103379</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>148879</t>
+          <t>146454</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>158228</t>
+          <t>158789</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>198612</t>
+          <t>199051</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>79171</t>
+          <t>79496</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>113046</t>
+          <t>111027</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>249334</t>
+          <t>250055</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>300839</t>
+          <t>302459</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,29%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>14700</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>14967</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23453</t>
+          <t>23476</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16576</t>
+          <t>16242</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13790</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>7558</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>24664</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38208</t>
+          <t>38565</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>30850</t>
+          <t>30393</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>54407</t>
+          <t>54513</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22154</t>
+          <t>22627</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>42796</t>
+          <t>43170</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23021</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>34222</t>
+          <t>34173</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>60482</t>
+          <t>59367</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>68292</t>
+          <t>68363</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>93600</t>
+          <t>94177</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18025</t>
+          <t>18268</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>34501</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>90742</t>
+          <t>91718</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>121720</t>
+          <t>122465</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -4254,97 +4254,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4480,97 +4480,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>44688</t>
+          <t>44843</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>76863</t>
+          <t>76887</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>45780</t>
+          <t>46453</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>77034</t>
+          <t>76194</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>99351</t>
+          <t>96706</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>139908</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>57682</t>
+          <t>59406</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>95795</t>
+          <t>95850</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>48996</t>
+          <t>49205</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>83273</t>
+          <t>80445</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>116612</t>
+          <t>114879</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>166829</t>
+          <t>164835</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>258688</t>
+          <t>259390</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>324586</t>
+          <t>319812</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>173078</t>
+          <t>173678</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>225076</t>
+          <t>224700</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>448801</t>
+          <t>449396</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>532615</t>
+          <t>530917</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>293788</t>
+          <t>290681</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>358025</t>
+          <t>357649</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>173066</t>
+          <t>173052</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>223797</t>
+          <t>226030</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>480259</t>
+          <t>482769</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>567195</t>
+          <t>562307</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>628332</t>
+          <t>629882</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>706236</t>
+          <t>707062</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>391805</t>
+          <t>392031</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>456934</t>
+          <t>455033</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1041204</t>
+          <t>1040461</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1136814</t>
+          <t>1144728</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,53%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2016</t>
+          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>10539</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16044</t>
+          <t>13561</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>17125</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20301</t>
+          <t>20808</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>16018</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35431</t>
+          <t>34066</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16040</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32409</t>
+          <t>32939</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15538</t>
+          <t>15602</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31993</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34752</t>
+          <t>34985</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59122</t>
+          <t>58793</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11307</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25779</t>
+          <t>25475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>35040</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32373</t>
+          <t>32127</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>54529</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18047</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34533</t>
+          <t>34503</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17223</t>
+          <t>15926</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33609</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37692</t>
+          <t>39083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62111</t>
+          <t>63762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27534</t>
+          <t>27848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30072</t>
+          <t>29822</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28616</t>
+          <t>28547</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54375</t>
+          <t>52132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22988</t>
+          <t>23838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45177</t>
+          <t>47781</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>21661</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41720</t>
+          <t>42527</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50442</t>
+          <t>48724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81041</t>
+          <t>79743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69647</t>
+          <t>69478</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>101608</t>
+          <t>100660</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51348</t>
+          <t>51292</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78172</t>
+          <t>78056</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>129567</t>
+          <t>129841</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>169944</t>
+          <t>169731</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74036</t>
+          <t>73490</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106547</t>
+          <t>106225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56248</t>
+          <t>56645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84470</t>
+          <t>83797</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139017</t>
+          <t>139068</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>180719</t>
+          <t>182022</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101043</t>
+          <t>102586</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136785</t>
+          <t>136700</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73439</t>
+          <t>74441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104570</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>183851</t>
+          <t>183106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>233218</t>
+          <t>229363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15169</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33821</t>
+          <t>33328</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34815</t>
+          <t>33337</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35428</t>
+          <t>34790</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62144</t>
+          <t>60656</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30991</t>
+          <t>30837</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55688</t>
+          <t>54979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27962</t>
+          <t>28876</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50282</t>
+          <t>52192</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66147</t>
+          <t>65929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>100539</t>
+          <t>99472</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97256</t>
+          <t>96858</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134643</t>
+          <t>135311</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52915</t>
+          <t>52415</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82980</t>
+          <t>81420</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>159135</t>
+          <t>158290</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>203712</t>
+          <t>206684</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89981</t>
+          <t>92498</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>130770</t>
+          <t>129909</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73343</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103351</t>
+          <t>103922</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>174773</t>
+          <t>174842</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>225102</t>
+          <t>223557</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148321</t>
+          <t>147671</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190060</t>
+          <t>187895</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84792</t>
+          <t>86125</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>119414</t>
+          <t>120080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>245381</t>
+          <t>241962</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>298046</t>
+          <t>295785</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14596</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33986</t>
+          <t>34130</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,47 +8483,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>9,28%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>22475</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>14094</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>32538</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>9,24%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>22475</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>14866</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>33403</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33243</t>
+          <t>33418</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60965</t>
+          <t>60470</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22865</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46935</t>
+          <t>46825</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22846</t>
+          <t>22802</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45289</t>
+          <t>44636</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50936</t>
+          <t>51109</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>81599</t>
+          <t>85211</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>80051</t>
+          <t>80278</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>116424</t>
+          <t>115375</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37776</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63304</t>
+          <t>64130</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>125116</t>
+          <t>124869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>168924</t>
+          <t>170485</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85774</t>
+          <t>87752</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120830</t>
+          <t>124613</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58035</t>
+          <t>57029</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86464</t>
+          <t>87326</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152904</t>
+          <t>151276</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>200328</t>
+          <t>196827</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>94168</t>
+          <t>94096</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131715</t>
+          <t>130320</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53790</t>
+          <t>53948</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>83482</t>
+          <t>82465</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>155295</t>
+          <t>155597</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>201434</t>
+          <t>201902</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24502</t>
+          <t>23419</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>10472</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27395</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22849</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>44917</t>
+          <t>46010</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10777</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28084</t>
+          <t>26778</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21278</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20688</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27918</t>
+          <t>28687</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50281</t>
+          <t>51684</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37115</t>
+          <t>35779</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>51256</t>
+          <t>50233</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80353</t>
+          <t>80393</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30475</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>52218</t>
+          <t>52614</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28722</t>
+          <t>28200</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>45749</t>
+          <t>45870</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>73982</t>
+          <t>73572</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>43237</t>
+          <t>42227</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>66962</t>
+          <t>68238</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41474</t>
+          <t>41100</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>70650</t>
+          <t>69741</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>102742</t>
+          <t>103269</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -9832,97 +9832,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>19,65%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>77,59%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>1020</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>4248</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>19,65%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>4186</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>81,84%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>4251</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -9980,62 +9980,62 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>4590</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>10,12%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -10058,97 +10058,97 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>905</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>4037</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>77,79%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>905</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>3827</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>17,44%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>8,72%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>73,73%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>3939</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>39,75%</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>949</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,31%</t>
         </is>
       </c>
     </row>
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,57%</t>
         </is>
       </c>
     </row>
@@ -10514,97 +10514,97 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -10627,97 +10627,97 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
           <t>795</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
+      <c r="W41" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -10740,97 +10740,97 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="W42" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -10853,97 +10853,97 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -10966,97 +10966,97 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="W44" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>65168</t>
+          <t>63831</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>101431</t>
+          <t>102604</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>73965</t>
+          <t>73450</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>110892</t>
+          <t>109459</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>146978</t>
+          <t>148285</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>199217</t>
+          <t>196159</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>116073</t>
+          <t>116065</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>162466</t>
+          <t>161761</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>106431</t>
+          <t>108633</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>148650</t>
+          <t>150378</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>237554</t>
+          <t>232820</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>300488</t>
+          <t>296757</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>327380</t>
+          <t>325332</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>391865</t>
+          <t>393512</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>202857</t>
+          <t>205956</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>259802</t>
+          <t>261059</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>546345</t>
+          <t>543659</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>632491</t>
+          <t>633200</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>327511</t>
+          <t>332091</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>397596</t>
+          <t>397521</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>245695</t>
+          <t>248417</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>302439</t>
+          <t>303396</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>593072</t>
+          <t>596597</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>682836</t>
+          <t>685202</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>444873</t>
+          <t>447229</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>518906</t>
+          <t>520952</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>287597</t>
+          <t>283995</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>344681</t>
+          <t>342580</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>749019</t>
+          <t>749016</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>844109</t>
+          <t>844967</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6713-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6713-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>16506</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>902</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27330</t>
+          <t>27962</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27509</t>
+          <t>28019</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27447</t>
+          <t>26840</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31894</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20946</t>
+          <t>21621</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26351</t>
+          <t>25445</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48269</t>
+          <t>48426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24648</t>
+          <t>25597</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43201</t>
+          <t>44469</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40321</t>
+          <t>39943</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59065</t>
+          <t>58825</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>70045</t>
+          <t>68795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>96957</t>
+          <t>96461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,53%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>10541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26969</t>
+          <t>27519</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29263</t>
+          <t>28293</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24142</t>
+          <t>25572</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48604</t>
+          <t>49431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>12385</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31023</t>
+          <t>30074</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11468</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28873</t>
+          <t>29158</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27888</t>
+          <t>27957</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53972</t>
+          <t>53710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69989</t>
+          <t>69112</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102202</t>
+          <t>102522</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31751</t>
+          <t>32104</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56822</t>
+          <t>57425</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>110233</t>
+          <t>108569</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>153368</t>
+          <t>150566</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62727</t>
+          <t>63246</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94486</t>
+          <t>94307</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54115</t>
+          <t>54276</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83520</t>
+          <t>83199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125469</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169273</t>
+          <t>169175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>160233</t>
+          <t>163256</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200405</t>
+          <t>202472</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108650</t>
+          <t>108183</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142802</t>
+          <t>143625</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>278793</t>
+          <t>280354</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332508</t>
+          <t>332174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27798</t>
+          <t>27055</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20888</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43649</t>
+          <t>43196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16928</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39271</t>
+          <t>39240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>10556</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>28266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32372</t>
+          <t>31032</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57996</t>
+          <t>57793</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71643</t>
+          <t>70229</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>105641</t>
+          <t>103474</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51231</t>
+          <t>52388</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80495</t>
+          <t>79376</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>130769</t>
+          <t>130026</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176485</t>
+          <t>175244</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90066</t>
+          <t>90374</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>126691</t>
+          <t>127670</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47648</t>
+          <t>47275</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74920</t>
+          <t>75730</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>145752</t>
+          <t>147662</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>191053</t>
+          <t>193311</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>168774</t>
+          <t>170929</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211386</t>
+          <t>211398</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>105121</t>
+          <t>109461</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>141357</t>
+          <t>142107</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>289637</t>
+          <t>289656</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>343206</t>
+          <t>342721</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,27%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9563</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>27448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>21481</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20486</t>
+          <t>19543</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43169</t>
+          <t>41793</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>11254</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28803</t>
+          <t>29323</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>10578</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>29248</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25985</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51912</t>
+          <t>51733</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>54495</t>
+          <t>51810</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>86176</t>
+          <t>85596</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42253</t>
+          <t>41152</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>68519</t>
+          <t>68794</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>102561</t>
+          <t>103759</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>144736</t>
+          <t>145302</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68157</t>
+          <t>66686</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>103846</t>
+          <t>100557</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30339</t>
+          <t>29055</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58011</t>
+          <t>58149</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>103379</t>
+          <t>105314</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>146454</t>
+          <t>150653</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>158789</t>
+          <t>159405</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>199051</t>
+          <t>201070</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>79496</t>
+          <t>80012</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111027</t>
+          <t>113942</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>250055</t>
+          <t>250096</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>302459</t>
+          <t>301620</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,15%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>14312</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14967</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23476</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>16038</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>13336</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>24664</t>
+          <t>23771</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18202</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9237</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>22036</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>30393</t>
+          <t>30862</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>54513</t>
+          <t>55174</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22627</t>
+          <t>22496</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43170</t>
+          <t>43878</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9511</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23718</t>
+          <t>22656</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>34173</t>
+          <t>35485</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>59367</t>
+          <t>58911</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>68363</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>94177</t>
+          <t>93657</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18268</t>
+          <t>18400</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34501</t>
+          <t>34062</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>91718</t>
+          <t>92510</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>122465</t>
+          <t>123104</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,75%</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>68,83%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>44843</t>
+          <t>45365</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>76887</t>
+          <t>76903</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>46453</t>
+          <t>45423</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>76194</t>
+          <t>77776</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>96706</t>
+          <t>99184</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>139908</t>
+          <t>143265</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>59406</t>
+          <t>59952</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>95850</t>
+          <t>95520</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>49205</t>
+          <t>48629</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>80445</t>
+          <t>82204</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>114879</t>
+          <t>116201</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>164835</t>
+          <t>165514</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>259390</t>
+          <t>257683</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>319812</t>
+          <t>321132</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>173678</t>
+          <t>174840</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>224700</t>
+          <t>227362</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>449396</t>
+          <t>443412</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>530917</t>
+          <t>529327</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>290681</t>
+          <t>293432</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>357649</t>
+          <t>356761</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>173052</t>
+          <t>174130</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>226030</t>
+          <t>225532</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>482769</t>
+          <t>483511</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>562307</t>
+          <t>568824</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>629882</t>
+          <t>623768</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>707062</t>
+          <t>701651</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>392031</t>
+          <t>391152</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>455033</t>
+          <t>453425</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1040461</t>
+          <t>1032744</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1144728</t>
+          <t>1139157</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>17803</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20808</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16018</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34066</t>
+          <t>33106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16040</t>
+          <t>15554</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32939</t>
+          <t>31660</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15602</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31390</t>
+          <t>32206</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34985</t>
+          <t>34954</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58793</t>
+          <t>58196</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25475</t>
+          <t>26003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18148</t>
+          <t>18592</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35040</t>
+          <t>35908</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32127</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54529</t>
+          <t>54960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34503</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15926</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33082</t>
+          <t>33682</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39083</t>
+          <t>39705</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63762</t>
+          <t>62398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27848</t>
+          <t>29010</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>13518</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29822</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>27921</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52132</t>
+          <t>52829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23838</t>
+          <t>22626</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47781</t>
+          <t>45511</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21661</t>
+          <t>20943</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42527</t>
+          <t>41920</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48724</t>
+          <t>50098</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79743</t>
+          <t>80545</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69478</t>
+          <t>69640</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100660</t>
+          <t>101174</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51292</t>
+          <t>52233</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78056</t>
+          <t>79670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>129841</t>
+          <t>127023</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>169731</t>
+          <t>171014</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>74172</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106225</t>
+          <t>107068</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56645</t>
+          <t>57880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83797</t>
+          <t>84858</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139068</t>
+          <t>137686</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182022</t>
+          <t>181094</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102586</t>
+          <t>102498</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136700</t>
+          <t>136730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74441</t>
+          <t>73181</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>103408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>183106</t>
+          <t>184443</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>229363</t>
+          <t>230231</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>15141</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33328</t>
+          <t>34425</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15135</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33337</t>
+          <t>34239</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34790</t>
+          <t>35049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60656</t>
+          <t>62772</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30837</t>
+          <t>30498</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54979</t>
+          <t>55518</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28876</t>
+          <t>28427</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52192</t>
+          <t>50112</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65929</t>
+          <t>64103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>99472</t>
+          <t>98620</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96858</t>
+          <t>94616</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135311</t>
+          <t>135267</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52415</t>
+          <t>52946</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81420</t>
+          <t>81377</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>158290</t>
+          <t>158262</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>206684</t>
+          <t>205667</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92498</t>
+          <t>92530</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>129909</t>
+          <t>130172</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72285</t>
+          <t>71994</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103922</t>
+          <t>104450</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>174842</t>
+          <t>173369</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>223557</t>
+          <t>221661</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>147671</t>
+          <t>148138</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187895</t>
+          <t>191664</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86125</t>
+          <t>85410</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>120080</t>
+          <t>118002</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>241962</t>
+          <t>245175</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>295785</t>
+          <t>298943</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>14994</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34130</t>
+          <t>34594</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>14304</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32538</t>
+          <t>34068</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33418</t>
+          <t>34344</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60470</t>
+          <t>61697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22705</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46825</t>
+          <t>45806</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22802</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44636</t>
+          <t>43938</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51109</t>
+          <t>51306</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>85211</t>
+          <t>82931</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>80278</t>
+          <t>80992</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>115375</t>
+          <t>116267</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38978</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64130</t>
+          <t>64101</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>124869</t>
+          <t>126119</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>170485</t>
+          <t>170921</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87752</t>
+          <t>87019</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124613</t>
+          <t>121613</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57029</t>
+          <t>58070</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87326</t>
+          <t>87437</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>151276</t>
+          <t>153118</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>196827</t>
+          <t>197865</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>94096</t>
+          <t>93268</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130320</t>
+          <t>129708</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53948</t>
+          <t>53563</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>82465</t>
+          <t>82987</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>155597</t>
+          <t>154324</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>201902</t>
+          <t>202408</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23419</t>
+          <t>23548</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26958</t>
+          <t>27548</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22044</t>
+          <t>20995</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46010</t>
+          <t>43479</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26778</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21226</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>20246</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41429</t>
+          <t>42713</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28687</t>
+          <t>28069</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51684</t>
+          <t>50958</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35779</t>
+          <t>38217</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>50233</t>
+          <t>50678</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80393</t>
+          <t>80330</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28601</t>
+          <t>28279</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>52614</t>
+          <t>51813</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28200</t>
+          <t>28760</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>45870</t>
+          <t>45702</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>73572</t>
+          <t>73469</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>42227</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>68238</t>
+          <t>66288</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>22148</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41100</t>
+          <t>41492</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>69741</t>
+          <t>69309</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>103269</t>
+          <t>101969</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>960</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>63831</t>
+          <t>66025</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>102604</t>
+          <t>101795</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>73450</t>
+          <t>73878</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>109459</t>
+          <t>111489</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>148285</t>
+          <t>147281</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>196159</t>
+          <t>197846</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>116065</t>
+          <t>116574</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>161761</t>
+          <t>159448</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>108633</t>
+          <t>107398</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>150378</t>
+          <t>148753</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>232820</t>
+          <t>234440</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>296757</t>
+          <t>296368</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>325332</t>
+          <t>323701</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>393512</t>
+          <t>388731</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>205956</t>
+          <t>204902</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>261059</t>
+          <t>256757</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>543659</t>
+          <t>548109</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>633200</t>
+          <t>635571</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>332091</t>
+          <t>331235</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>397521</t>
+          <t>398886</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>248417</t>
+          <t>246418</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>303396</t>
+          <t>301678</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>596597</t>
+          <t>593924</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>685202</t>
+          <t>681850</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>447229</t>
+          <t>444076</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>520952</t>
+          <t>517126</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>283995</t>
+          <t>285770</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>342580</t>
+          <t>344400</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>749016</t>
+          <t>748429</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>844967</t>
+          <t>842989</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
